--- a/polls/026_scheduling_poll--polls.xlsx
+++ b/polls/026_scheduling_poll--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>start_date_1</t>
+          <t>start_date_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>start_time_1</t>
+          <t>start_time_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>end_date_1</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>end_time_1</t>
+          <t>end_date_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>End Time</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>location_1</t>
+          <t>end_time_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>End Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>description_1</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>attendees_1</t>
+          <t>attendees_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>repeat_1</t>
+          <t>repeat_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>timezone_1</t>
+          <t>timezone_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reminders_1</t>
+          <t>reminders_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reminder_frequency_1</t>
+          <t>reminder_frequency_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reminder_send_method_1</t>
+          <t>reminder_send_method_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>poll_reminder_senders_1</t>
+          <t>poll_reminder_senders_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>poll_reminder_body_2</t>
+          <t>poll_reminder_senders_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poll Reminder Body</t>
+          <t>Poll Reminder Senders 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>poll_reminder_body_3</t>
+          <t>poll_reminder_sender_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poll Reminder Body</t>
+          <t>Poll Reminder Sender 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>poll_reminder_senders_2</t>
+          <t>poll_reminder_sender_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poll Reminder Senders</t>
+          <t>Poll Reminder Sender 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>poll_reminder_sender_1</t>
+          <t>poll_reminder_sender_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poll Reminder Sender 1</t>
+          <t>Poll Reminder Sender 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>poll_reminder_sender_2</t>
+          <t>poll_reminder_sender_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poll Reminder Sender 2</t>
+          <t>Poll Reminder Sender 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Poll Reminder Sender 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Poll Reminder Sender 4</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Poll Reminder Sender 5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Poll Reminder Sender 6</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Poll Reminder Sender 7</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,11 +983,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,284 +1033,284 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>attendees_1_choices</t>
+          <t>attendees_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>attendees_1_choices</t>
+          <t>attendees_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>repeat_1_choices</t>
+          <t>repeat_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>repeat_1_choices</t>
+          <t>repeat_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>timezone_1_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>timezone_1_choices</t>
+          <t>timezone_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>reminders_1_choices</t>
+          <t>reminders_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reminders_1_choices</t>
+          <t>reminders_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reminder_frequency_1_choices</t>
+          <t>reminder_frequency_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>reminder_frequency_1_choices</t>
+          <t>reminder_frequency_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reminder_send_method_1_choices</t>
+          <t>reminder_send_method_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reminder_send_method_1_choices</t>
+          <t>reminder_send_method_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>poll_reminder_senders_1_choices</t>
+          <t>poll_reminder_senders_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>poll_reminder_senders_1_choices</t>
+          <t>poll_reminder_senders_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>poll_reminder_senders_2_choices</t>
+          <t>poll_reminder_senders_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>poll_reminder_senders_2_choices</t>
+          <t>poll_reminder_senders_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1556,114 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_5_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_6_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_6_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_7_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>poll_reminder_sender_7_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
